--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ)cn.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="36">
   <si>
     <t>in practice</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -125,6 +125,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -145,11 +149,23 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
+    <t>PE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE均值</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>深创100ETF</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE均值</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -166,6 +182,10 @@
   </si>
   <si>
     <t>标志</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深创100ETF</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -655,7 +675,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -835,6 +855,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -844,7 +867,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1023,6 +1046,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -1066,7 +1092,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1246,6 +1272,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1255,7 +1284,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1435,6 +1464,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1978849.1612350328</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2022104.2217609019</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1477,7 +1509,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1657,6 +1689,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1666,7 +1701,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1846,6 +1881,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>820356.13175280904</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>863611.19227867806</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1867,11 +1905,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="401928960"/>
-        <c:axId val="401930496"/>
+        <c:axId val="453319680"/>
+        <c:axId val="453338624"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="401928960"/>
+        <c:axId val="453319680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1914,14 +1952,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401930496"/>
+        <c:crossAx val="453338624"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="401930496"/>
+        <c:axId val="453338624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1972,7 +2010,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401928960"/>
+        <c:crossAx val="453319680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2163,7 +2201,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2343,6 +2381,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-36057.366675283578</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-60139.263576626639</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2362,8 +2403,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="473132416"/>
-        <c:axId val="473130880"/>
+        <c:axId val="526873728"/>
+        <c:axId val="526871936"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2388,7 +2429,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2568,6 +2609,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2577,7 +2621,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2757,6 +2801,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2778,11 +2825,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="473127552"/>
-        <c:axId val="473129344"/>
+        <c:axId val="526868864"/>
+        <c:axId val="526870400"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="473127552"/>
+        <c:axId val="526868864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2825,14 +2872,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="473129344"/>
+        <c:crossAx val="526870400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="473129344"/>
+        <c:axId val="526870400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2883,12 +2930,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="473127552"/>
+        <c:crossAx val="526868864"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="473130880"/>
+        <c:axId val="526871936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2925,12 +2972,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="473132416"/>
+        <c:crossAx val="526873728"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="473132416"/>
+        <c:axId val="526873728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2939,7 +2986,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="473130880"/>
+        <c:crossAx val="526871936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3118,7 +3165,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3298,6 +3345,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3307,7 +3357,7 @@
               <c:f>'模型二 (2)PE副本成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3486,6 +3536,9 @@
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>8275639.9932962749</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
               </c:numCache>
@@ -3529,7 +3582,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3709,6 +3762,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3718,7 +3774,7 @@
               <c:f>'模型二 (2)PE副本成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3898,6 +3954,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>15803331.182775768</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>16174234.157067223</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3940,7 +3999,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4120,6 +4179,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4129,7 +4191,7 @@
               <c:f>'模型二 (2)PE副本成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4309,6 +4371,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>7527691.1894794926</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>7898594.1637709476</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4330,11 +4395,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="479472256"/>
-        <c:axId val="479474048"/>
+        <c:axId val="538116480"/>
+        <c:axId val="538118016"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="479472256"/>
+        <c:axId val="538116480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4377,14 +4442,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479474048"/>
+        <c:crossAx val="538118016"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="479474048"/>
+        <c:axId val="538118016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4435,7 +4500,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479472256"/>
+        <c:crossAx val="538116480"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4626,7 +4691,7 @@
               <c:f>'模型二 (2)PE副本成交量'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4806,6 +4871,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-228232.84251096987</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-703792.54386857653</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4825,8 +4893,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="479522816"/>
-        <c:axId val="479496448"/>
+        <c:axId val="538142208"/>
+        <c:axId val="538140672"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4851,7 +4919,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5031,6 +5099,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5040,7 +5111,7 @@
               <c:f>'模型二 (2)PE副本成交量'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5220,6 +5291,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5241,11 +5315,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="479489024"/>
-        <c:axId val="479494912"/>
+        <c:axId val="538137344"/>
+        <c:axId val="538138880"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="479489024"/>
+        <c:axId val="538137344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5288,14 +5362,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479494912"/>
+        <c:crossAx val="538138880"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="479494912"/>
+        <c:axId val="538138880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5346,12 +5420,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479489024"/>
+        <c:crossAx val="538137344"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="479496448"/>
+        <c:axId val="538140672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5388,12 +5462,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479522816"/>
+        <c:crossAx val="538142208"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="479522816"/>
+        <c:axId val="538142208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5402,7 +5476,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="479496448"/>
+        <c:crossAx val="538140672"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5581,7 +5655,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5761,6 +5835,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5770,7 +5847,7 @@
               <c:f>'模型二 (2)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5949,6 +6026,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -5992,7 +6072,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6172,6 +6252,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6181,7 +6264,7 @@
               <c:f>'模型二 (2)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6361,6 +6444,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>16470742.053078819</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>16842108.331714839</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6403,7 +6489,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6583,6 +6669,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6592,7 +6681,7 @@
               <c:f>'模型二 (2)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6772,6 +6861,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>7109407.2353513949</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>7480773.5139874145</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6793,11 +6885,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="480177152"/>
-        <c:axId val="494867200"/>
+        <c:axId val="538801280"/>
+        <c:axId val="538802816"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="480177152"/>
+        <c:axId val="538801280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6840,14 +6932,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494867200"/>
+        <c:crossAx val="538802816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="494867200"/>
+        <c:axId val="538802816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6898,7 +6990,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="480177152"/>
+        <c:crossAx val="538801280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7089,7 +7181,7 @@
               <c:f>'模型二 (2)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7269,6 +7361,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-329147.77001413936</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-915628.10722505616</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7288,8 +7383,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="494907776"/>
-        <c:axId val="494893696"/>
+        <c:axId val="539171072"/>
+        <c:axId val="539169536"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7314,7 +7409,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7494,6 +7589,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7503,7 +7601,7 @@
               <c:f>'模型二 (2)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7683,6 +7781,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7704,11 +7805,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="494886272"/>
-        <c:axId val="494892160"/>
+        <c:axId val="538879488"/>
+        <c:axId val="538881024"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="494886272"/>
+        <c:axId val="538879488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7751,14 +7852,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494892160"/>
+        <c:crossAx val="538881024"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="494892160"/>
+        <c:axId val="538881024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7809,12 +7910,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494886272"/>
+        <c:crossAx val="538879488"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="494893696"/>
+        <c:axId val="539169536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7851,12 +7952,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494907776"/>
+        <c:crossAx val="539171072"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="494907776"/>
+        <c:axId val="539171072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7865,7 +7966,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="494893696"/>
+        <c:crossAx val="539169536"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8027,7 +8128,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8207,6 +8308,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-36057.366675283578</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-60139.263576626639</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8226,8 +8330,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="546469760"/>
-        <c:axId val="546467840"/>
+        <c:axId val="460892416"/>
+        <c:axId val="453371392"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8252,7 +8356,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8432,6 +8536,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8441,7 +8548,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8621,6 +8728,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8642,11 +8752,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="546463744"/>
-        <c:axId val="546466048"/>
+        <c:axId val="453367680"/>
+        <c:axId val="453369216"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="546463744"/>
+        <c:axId val="453367680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8689,14 +8799,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="546466048"/>
+        <c:crossAx val="453369216"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="546466048"/>
+        <c:axId val="453369216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8747,12 +8857,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="546463744"/>
+        <c:crossAx val="453367680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="546467840"/>
+        <c:axId val="453371392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8789,12 +8899,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="546469760"/>
+        <c:crossAx val="460892416"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="546469760"/>
+        <c:axId val="460892416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8803,7 +8913,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="546467840"/>
+        <c:crossAx val="453371392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8982,7 +9092,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9162,6 +9272,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9171,7 +9284,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9350,6 +9463,9 @@
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>1319891.5920995933</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
               </c:numCache>
@@ -9393,7 +9509,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9573,6 +9689,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9582,7 +9701,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9762,6 +9881,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>2247575.650286919</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2300222.1250249241</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9804,7 +9926,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9984,6 +10106,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9993,7 +10118,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10173,6 +10298,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>927684.05818732572</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>980330.5329253308</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10194,11 +10322,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="556770432"/>
-        <c:axId val="556771968"/>
+        <c:axId val="461279232"/>
+        <c:axId val="461281536"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="556770432"/>
+        <c:axId val="461279232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10241,14 +10369,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556771968"/>
+        <c:crossAx val="461281536"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="556771968"/>
+        <c:axId val="461281536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10299,7 +10427,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556770432"/>
+        <c:crossAx val="461279232"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10511,7 +10639,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10691,6 +10819,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-36057.366675283578</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-60139.263576626639</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10710,8 +10841,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="571171968"/>
-        <c:axId val="571059584"/>
+        <c:axId val="539245184"/>
+        <c:axId val="539243648"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10736,7 +10867,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10916,6 +11047,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10925,7 +11059,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -11105,6 +11239,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11126,11 +11263,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="571056128"/>
-        <c:axId val="571057664"/>
+        <c:axId val="538683264"/>
+        <c:axId val="538853376"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="571056128"/>
+        <c:axId val="538683264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11173,14 +11310,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="571057664"/>
+        <c:crossAx val="538853376"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="571057664"/>
+        <c:axId val="538853376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11231,12 +11368,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="571056128"/>
+        <c:crossAx val="538683264"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="571059584"/>
+        <c:axId val="539243648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11273,12 +11410,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="571171968"/>
+        <c:crossAx val="539245184"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="571171968"/>
+        <c:axId val="539245184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11287,7 +11424,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="571059584"/>
+        <c:crossAx val="539243648"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11466,7 +11603,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11646,6 +11783,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11655,7 +11795,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11834,6 +11974,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -11877,7 +12020,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12057,6 +12200,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12066,7 +12212,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12246,6 +12392,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>19051655.379257303</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>19503027.168851279</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12288,7 +12437,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12468,6 +12617,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12477,7 +12629,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12657,6 +12809,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>8163819.6057763249</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>8615191.3953703009</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12678,11 +12833,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="571383168"/>
-        <c:axId val="571475456"/>
+        <c:axId val="544153984"/>
+        <c:axId val="544155904"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="571383168"/>
+        <c:axId val="544153984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12725,14 +12880,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="571475456"/>
+        <c:crossAx val="544155904"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="571475456"/>
+        <c:axId val="544155904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12783,7 +12938,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="571383168"/>
+        <c:crossAx val="544153984"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12995,7 +13150,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13175,6 +13330,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-329147.77001413936</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-915628.10722505616</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13194,8 +13352,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="573039360"/>
-        <c:axId val="572984320"/>
+        <c:axId val="546260480"/>
+        <c:axId val="545561984"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -13220,7 +13378,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13400,6 +13558,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13409,7 +13570,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -13589,6 +13750,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13610,11 +13774,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="572972032"/>
-        <c:axId val="572982784"/>
+        <c:axId val="545558528"/>
+        <c:axId val="545560064"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="572972032"/>
+        <c:axId val="545558528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13657,14 +13821,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="572982784"/>
+        <c:crossAx val="545560064"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="572982784"/>
+        <c:axId val="545560064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13715,12 +13879,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="572972032"/>
+        <c:crossAx val="545558528"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="572984320"/>
+        <c:axId val="545561984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13757,12 +13921,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="573039360"/>
+        <c:crossAx val="546260480"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="573039360"/>
+        <c:axId val="546260480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13771,7 +13935,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="572984320"/>
+        <c:crossAx val="545561984"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13950,7 +14114,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14130,6 +14294,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14139,7 +14306,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14318,6 +14485,9 @@
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>1319095.5916679052</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
               </c:numCache>
@@ -14361,7 +14531,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14541,6 +14711,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14550,7 +14723,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14730,6 +14903,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>2518827.8975449791</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2579594.8543026936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14772,7 +14948,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14952,6 +15128,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14961,7 +15140,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15141,6 +15320,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1199732.3058770739</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1260499.2626347884</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15162,11 +15344,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="573676928"/>
-        <c:axId val="573854848"/>
+        <c:axId val="546462720"/>
+        <c:axId val="546489472"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="573676928"/>
+        <c:axId val="546462720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15209,14 +15391,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="573854848"/>
+        <c:crossAx val="546489472"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="573854848"/>
+        <c:axId val="546489472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15267,7 +15449,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="573676928"/>
+        <c:crossAx val="546462720"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15458,7 +15640,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15638,6 +15820,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-31779.256552160365</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-97996.430158915711</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15657,8 +15842,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="470891520"/>
-        <c:axId val="470889984"/>
+        <c:axId val="547525376"/>
+        <c:axId val="547490816"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -15683,7 +15868,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15863,6 +16048,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15872,7 +16060,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -16052,6 +16240,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16073,11 +16264,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="470825216"/>
-        <c:axId val="470888448"/>
+        <c:axId val="547259520"/>
+        <c:axId val="547488128"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="470825216"/>
+        <c:axId val="547259520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16120,14 +16311,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="470888448"/>
+        <c:crossAx val="547488128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="470888448"/>
+        <c:axId val="547488128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16178,12 +16369,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="470825216"/>
+        <c:crossAx val="547259520"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="470889984"/>
+        <c:axId val="547490816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16220,12 +16411,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="470891520"/>
+        <c:crossAx val="547525376"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="470891520"/>
+        <c:axId val="547525376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16234,7 +16425,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="470889984"/>
+        <c:crossAx val="547490816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -16413,7 +16604,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16593,6 +16784,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16602,7 +16796,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16781,6 +16975,9 @@
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>1174811.7958955525</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
               </c:numCache>
@@ -16824,7 +17021,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -17004,6 +17201,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17013,7 +17213,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17193,6 +17393,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>2010615.8177554612</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2054661.8557303001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17235,7 +17438,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -17415,6 +17618,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17424,7 +17630,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17604,6 +17810,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>835804.02185990871</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>879850.05983474758</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17625,11 +17834,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="472271104"/>
-        <c:axId val="473112576"/>
+        <c:axId val="514912256"/>
+        <c:axId val="514913792"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="472271104"/>
+        <c:axId val="514912256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17672,14 +17881,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="473112576"/>
+        <c:crossAx val="514913792"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="473112576"/>
+        <c:axId val="514913792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17730,7 +17939,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472271104"/>
+        <c:crossAx val="514912256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17831,7 +18040,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17869,7 +18078,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17912,7 +18121,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17950,7 +18159,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17993,7 +18202,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18031,7 +18240,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18074,7 +18283,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18112,7 +18321,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18155,7 +18364,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18193,7 +18402,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18236,7 +18445,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18274,7 +18483,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18317,7 +18526,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18355,7 +18564,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18666,7 +18875,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -18797,28 +19006,28 @@
       </c>
       <c r="M3" s="27"/>
       <c r="P3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -21307,6 +21516,44 @@
       </c>
       <c r="L62" s="29">
         <v>241671.12627942342</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="32">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="31">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="29">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="29">
+        <v>-60139.263576626639</v>
+      </c>
+      <c r="F63" s="30">
+        <v>-47131.083462289775</v>
+      </c>
+      <c r="G63" s="30">
+        <v>1348192.6340495073</v>
+      </c>
+      <c r="H63" s="30">
+        <v>1720293.8319048518</v>
+      </c>
+      <c r="I63" s="30">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J63" s="30">
+        <v>2022104.2217609019</v>
+      </c>
+      <c r="K63" s="30">
+        <v>863611.19227867806</v>
+      </c>
+      <c r="L63" s="29">
+        <v>301810.38985605008</v>
       </c>
     </row>
   </sheetData>
@@ -21325,7 +21572,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH62"/>
+  <dimension ref="A1:AH63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -21360,16 +21607,16 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -21396,16 +21643,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N1" s="44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -21467,28 +21714,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -24666,6 +24913,56 @@
         <v>86.230028778736084</v>
       </c>
       <c r="P62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="16">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="17">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="17">
+        <v>-60139.263576626639</v>
+      </c>
+      <c r="F63" s="18">
+        <v>-47131.083462289775</v>
+      </c>
+      <c r="G63" s="18">
+        <v>1651141.3025257313</v>
+      </c>
+      <c r="H63" s="18">
+        <v>2106856.3398144585</v>
+      </c>
+      <c r="I63" s="18">
+        <v>1319891.5920995933</v>
+      </c>
+      <c r="J63" s="18">
+        <v>2300222.1250249241</v>
+      </c>
+      <c r="K63" s="18">
+        <v>980330.5329253308</v>
+      </c>
+      <c r="L63" s="17">
+        <v>193365.78521046543</v>
+      </c>
+      <c r="M63" s="22">
+        <v>4.3435412055936783E-2</v>
+      </c>
+      <c r="N63" s="22">
+        <v>5.037156159067379E-2</v>
+      </c>
+      <c r="O63" s="22">
+        <v>86.230028778736084</v>
+      </c>
+      <c r="P63" s="1">
         <v>1</v>
       </c>
     </row>
@@ -24685,7 +24982,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH62"/>
+  <dimension ref="A1:AH63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24720,10 +25017,10 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>3</v>
@@ -24756,16 +25053,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N1" s="44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -24827,28 +25124,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -28026,6 +28323,56 @@
         <v>86.230028778736084</v>
       </c>
       <c r="P62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="16">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="17">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="17">
+        <v>-915628.10722505616</v>
+      </c>
+      <c r="F63" s="18">
+        <v>-717576.87366851489</v>
+      </c>
+      <c r="G63" s="18">
+        <v>13842794.925130703</v>
+      </c>
+      <c r="H63" s="18">
+        <v>17663406.641303208</v>
+      </c>
+      <c r="I63" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J63" s="18">
+        <v>19503027.168851279</v>
+      </c>
+      <c r="K63" s="18">
+        <v>8615191.3953703009</v>
+      </c>
+      <c r="L63" s="17">
+        <v>1839620.5275480719</v>
+      </c>
+      <c r="M63" s="22">
+        <v>4.3435412055936783E-2</v>
+      </c>
+      <c r="N63" s="22">
+        <v>5.037156159067379E-2</v>
+      </c>
+      <c r="O63" s="22">
+        <v>86.230028778736084</v>
+      </c>
+      <c r="P63" s="1">
         <v>1</v>
       </c>
     </row>
@@ -28045,7 +28392,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ62"/>
+  <dimension ref="A1:AJ63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -28080,10 +28427,10 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>3</v>
@@ -28092,10 +28439,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -28122,16 +28469,16 @@
         <v>12</v>
       </c>
       <c r="O1" s="44" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P1" s="44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Q1" s="48" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -28205,28 +28552,28 @@
       <c r="P3" s="22"/>
       <c r="Q3" s="22"/>
       <c r="S3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -31758,6 +32105,62 @@
         <v>86.230028778736084</v>
       </c>
       <c r="R62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="16">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="17">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="17">
+        <v>3094800</v>
+      </c>
+      <c r="F63" s="17">
+        <v>4026308.4497372219</v>
+      </c>
+      <c r="G63" s="17">
+        <v>-97996.430158915711</v>
+      </c>
+      <c r="H63" s="18">
+        <v>-76799.708778299275</v>
+      </c>
+      <c r="I63" s="18">
+        <v>1883423.5569906416</v>
+      </c>
+      <c r="J63" s="18">
+        <v>2403248.501828203</v>
+      </c>
+      <c r="K63" s="18">
+        <v>1319095.5916679052</v>
+      </c>
+      <c r="L63" s="18">
+        <v>2579594.8543026936</v>
+      </c>
+      <c r="M63" s="18">
+        <v>1260499.2626347884</v>
+      </c>
+      <c r="N63" s="17">
+        <v>176346.35247449053</v>
+      </c>
+      <c r="O63" s="22">
+        <v>4.3435412055936783E-2</v>
+      </c>
+      <c r="P63" s="22">
+        <v>5.037156159067379E-2</v>
+      </c>
+      <c r="Q63" s="22">
+        <v>86.230028778736084</v>
+      </c>
+      <c r="R63" s="1">
         <v>1</v>
       </c>
     </row>
@@ -31777,7 +32180,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ62"/>
+  <dimension ref="A1:AJ63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -31812,10 +32215,10 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>3</v>
@@ -31848,19 +32251,19 @@
         <v>12</v>
       </c>
       <c r="M1" s="48" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="N1" s="48" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="P1" s="48" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -31938,28 +32341,28 @@
         <v>1</v>
       </c>
       <c r="S3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -35317,6 +35720,59 @@
         <v>94.913940221952458</v>
       </c>
       <c r="Q62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="16">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="17">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="17">
+        <v>-60139.263576626639</v>
+      </c>
+      <c r="F63" s="18">
+        <v>-47131.083462289775</v>
+      </c>
+      <c r="G63" s="18">
+        <v>1373708.0207151792</v>
+      </c>
+      <c r="H63" s="18">
+        <v>1752851.46587425</v>
+      </c>
+      <c r="I63" s="18">
+        <v>1174811.7958955525</v>
+      </c>
+      <c r="J63" s="18">
+        <v>2054661.8557303001</v>
+      </c>
+      <c r="K63" s="18">
+        <v>879850.05983474758</v>
+      </c>
+      <c r="L63" s="17">
+        <v>301810.38985605008</v>
+      </c>
+      <c r="M63" s="21">
+        <v>93.931398043426469</v>
+      </c>
+      <c r="N63" s="21">
+        <v>87.037193073217864</v>
+      </c>
+      <c r="O63" s="21">
+        <v>83.098819498850574</v>
+      </c>
+      <c r="P63" s="21">
+        <v>94.913940221952458</v>
+      </c>
+      <c r="Q63" s="1">
         <v>1</v>
       </c>
     </row>
@@ -35336,7 +35792,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ62"/>
+  <dimension ref="A1:AJ63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -35371,10 +35827,10 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>3</v>
@@ -35383,10 +35839,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -35482,28 +35938,28 @@
       </c>
       <c r="O3" s="7"/>
       <c r="S3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -38346,6 +38802,50 @@
       </c>
       <c r="N62" s="17">
         <v>907397.80051921715</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="16">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="17">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="17">
+        <v>3094800</v>
+      </c>
+      <c r="F63" s="17">
+        <v>4026308.4497372219</v>
+      </c>
+      <c r="G63" s="17">
+        <v>-703792.54386857653</v>
+      </c>
+      <c r="H63" s="18">
+        <v>-551561.54486233124</v>
+      </c>
+      <c r="I63" s="18">
+        <v>11413043.535623506</v>
+      </c>
+      <c r="J63" s="18">
+        <v>14563043.812679429</v>
+      </c>
+      <c r="K63" s="18">
+        <v>8275639.9932962749</v>
+      </c>
+      <c r="L63" s="18">
+        <v>16174234.157067223</v>
+      </c>
+      <c r="M63" s="18">
+        <v>7898594.1637709476</v>
+      </c>
+      <c r="N63" s="17">
+        <v>1611190.3443877937</v>
       </c>
     </row>
   </sheetData>
@@ -38364,7 +38864,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -38399,16 +38899,16 @@
   <sheetData>
     <row r="1" spans="1:33" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>3</v>
-      </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -38495,28 +38995,28 @@
       </c>
       <c r="M3" s="7"/>
       <c r="P3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -41005,6 +41505,44 @@
       </c>
       <c r="L62" s="17">
         <v>1556201.7813372496</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="16">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="17">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="17">
+        <v>-915628.10722505616</v>
+      </c>
+      <c r="F63" s="18">
+        <v>-717576.87366851489</v>
+      </c>
+      <c r="G63" s="18">
+        <v>11261973.499519134</v>
+      </c>
+      <c r="H63" s="18">
+        <v>14370278.443152532</v>
+      </c>
+      <c r="I63" s="18">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J63" s="18">
+        <v>16842108.331714839</v>
+      </c>
+      <c r="K63" s="18">
+        <v>7480773.5139874145</v>
+      </c>
+      <c r="L63" s="17">
+        <v>2471829.8885623058</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ)cn.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="33">
   <si>
     <t>in practice</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -125,10 +125,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -149,7 +145,19 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>深创100ETF</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE均值</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -655,7 +663,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -841,6 +849,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -850,7 +861,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1035,6 +1046,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -1078,7 +1092,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1264,6 +1278,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1273,7 +1290,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1459,6 +1476,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1794259.6267486978</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1803474.034715408</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1501,7 +1521,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1687,6 +1707,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1696,7 +1719,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1882,6 +1905,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>635766.59726647404</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>644981.0052331842</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1903,11 +1929,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="697707904"/>
-        <c:axId val="697718656"/>
+        <c:axId val="159430912"/>
+        <c:axId val="159434240"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="697707904"/>
+        <c:axId val="159430912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1950,14 +1976,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="697718656"/>
+        <c:crossAx val="159434240"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="697718656"/>
+        <c:axId val="159434240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2008,7 +2034,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="697707904"/>
+        <c:crossAx val="159430912"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2199,7 +2225,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2385,6 +2411,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-35250.090060671617</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-34946.17272282279</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2404,8 +2433,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="692936064"/>
-        <c:axId val="692934528"/>
+        <c:axId val="494603648"/>
+        <c:axId val="494602112"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2430,7 +2459,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2616,6 +2645,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2625,7 +2657,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2811,6 +2843,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2832,11 +2867,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="692923008"/>
-        <c:axId val="692932992"/>
+        <c:axId val="494033536"/>
+        <c:axId val="494600576"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="692923008"/>
+        <c:axId val="494033536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2879,14 +2914,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692932992"/>
+        <c:crossAx val="494600576"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="692932992"/>
+        <c:axId val="494600576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2937,12 +2972,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692923008"/>
+        <c:crossAx val="494033536"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="692934528"/>
+        <c:axId val="494602112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2979,12 +3014,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692936064"/>
+        <c:crossAx val="494603648"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="692936064"/>
+        <c:axId val="494603648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2993,7 +3028,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="692934528"/>
+        <c:crossAx val="494602112"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3172,7 +3207,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3358,6 +3393,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3367,7 +3405,7 @@
               <c:f>'模型二 (2)PE副本成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3552,6 +3590,9 @@
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>8275639.9932962749</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
               </c:numCache>
@@ -3595,7 +3636,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3781,6 +3822,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3790,7 +3834,7 @@
               <c:f>'模型二 (2)PE副本成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3976,6 +4020,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>14245429.46213273</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>14323097.271860281</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4018,7 +4065,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4204,6 +4251,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4213,7 +4263,7 @@
               <c:f>'模型二 (2)PE副本成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4399,6 +4449,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>5969789.4688364547</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6047457.2785640061</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4420,11 +4473,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="692976256"/>
-        <c:axId val="692978048"/>
+        <c:axId val="494656128"/>
+        <c:axId val="494657920"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="692976256"/>
+        <c:axId val="494656128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4467,14 +4520,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692978048"/>
+        <c:crossAx val="494657920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="692978048"/>
+        <c:axId val="494657920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4525,7 +4578,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692976256"/>
+        <c:crossAx val="494656128"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4716,7 +4769,7 @@
               <c:f>'模型二 (2)PE副本成交量'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4902,6 +4955,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-351576.30531150417</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-130359.36832865544</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4921,8 +4977,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="693080064"/>
-        <c:axId val="693078272"/>
+        <c:axId val="495091712"/>
+        <c:axId val="495089920"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4947,7 +5003,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5133,6 +5189,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5142,7 +5201,7 @@
               <c:f>'模型二 (2)PE副本成交量'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5328,6 +5387,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5349,11 +5411,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="693058560"/>
-        <c:axId val="693076736"/>
+        <c:axId val="495082496"/>
+        <c:axId val="495088384"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="693058560"/>
+        <c:axId val="495082496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5396,14 +5458,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="693076736"/>
+        <c:crossAx val="495088384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="693076736"/>
+        <c:axId val="495088384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5454,12 +5516,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="693058560"/>
+        <c:crossAx val="495082496"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="693078272"/>
+        <c:axId val="495089920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5496,12 +5558,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="693080064"/>
+        <c:crossAx val="495091712"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="693080064"/>
+        <c:axId val="495091712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5510,7 +5572,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="693078272"/>
+        <c:crossAx val="495089920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5689,7 +5751,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5875,6 +5937,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5884,7 +5949,7 @@
               <c:f>'模型二 (2)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6069,6 +6134,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -6112,7 +6180,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6298,6 +6366,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6307,7 +6378,7 @@
               <c:f>'模型二 (2)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6493,6 +6564,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>14938834.477348203</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>15015678.778184865</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6535,7 +6609,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6721,6 +6795,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6730,7 +6807,7 @@
               <c:f>'模型二 (2)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6916,6 +6993,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>5577499.6596207786</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>5654343.9604574405</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6937,11 +7017,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="693152768"/>
-        <c:axId val="693502720"/>
+        <c:axId val="495148032"/>
+        <c:axId val="495174400"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="693152768"/>
+        <c:axId val="495148032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6984,14 +7064,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="693502720"/>
+        <c:crossAx val="495174400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="693502720"/>
+        <c:axId val="495174400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7042,7 +7122,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="693152768"/>
+        <c:crossAx val="495148032"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7233,7 +7313,7 @@
               <c:f>'模型二 (2)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7419,6 +7499,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-314574.39222416701</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-309173.41467680095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7438,8 +7521,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="693526912"/>
-        <c:axId val="693525120"/>
+        <c:axId val="495272320"/>
+        <c:axId val="495270528"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7464,7 +7547,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7650,6 +7733,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7659,7 +7745,7 @@
               <c:f>'模型二 (2)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7845,6 +7931,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7866,11 +7955,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="693521792"/>
-        <c:axId val="693523584"/>
+        <c:axId val="495259008"/>
+        <c:axId val="495268992"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="693521792"/>
+        <c:axId val="495259008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7913,14 +8002,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="693523584"/>
+        <c:crossAx val="495268992"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="693523584"/>
+        <c:axId val="495268992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7971,12 +8060,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="693521792"/>
+        <c:crossAx val="495259008"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="693525120"/>
+        <c:axId val="495270528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8013,12 +8102,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="693526912"/>
+        <c:crossAx val="495272320"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="693526912"/>
+        <c:axId val="495272320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8027,7 +8116,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="693525120"/>
+        <c:crossAx val="495270528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8189,7 +8278,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8375,6 +8464,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-35250.090060671617</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-34946.17272282279</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8394,8 +8486,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="697822208"/>
-        <c:axId val="697820672"/>
+        <c:axId val="494643456"/>
+        <c:axId val="494640512"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8420,7 +8512,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8606,6 +8698,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8615,7 +8710,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8801,6 +8896,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8822,11 +8920,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="697766272"/>
-        <c:axId val="697768192"/>
+        <c:axId val="494637056"/>
+        <c:axId val="494638592"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="697766272"/>
+        <c:axId val="494637056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8869,14 +8967,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="697768192"/>
+        <c:crossAx val="494638592"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="697768192"/>
+        <c:axId val="494638592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8927,12 +9025,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="697766272"/>
+        <c:crossAx val="494637056"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="697820672"/>
+        <c:axId val="494640512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8969,12 +9067,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="697822208"/>
+        <c:crossAx val="494643456"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="697822208"/>
+        <c:axId val="494643456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8983,7 +9081,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="697820672"/>
+        <c:crossAx val="494640512"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9162,7 +9260,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9348,6 +9446,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9357,7 +9458,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9542,6 +9643,9 @@
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>1319891.5920995933</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
               </c:numCache>
@@ -9585,7 +9689,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9771,6 +9875,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9780,7 +9887,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9966,6 +10073,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>2021179.1960838926</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2032514.2354846764</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10008,7 +10118,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10194,6 +10304,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10203,7 +10316,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10389,6 +10502,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>701287.60398429935</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>712622.64338508318</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10410,11 +10526,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="697930496"/>
-        <c:axId val="697932416"/>
+        <c:axId val="499052544"/>
+        <c:axId val="499054848"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="697930496"/>
+        <c:axId val="499052544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10457,14 +10573,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="697932416"/>
+        <c:crossAx val="499054848"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="697932416"/>
+        <c:axId val="499054848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10515,7 +10631,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="697930496"/>
+        <c:crossAx val="499052544"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10727,7 +10843,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10913,6 +11029,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-35250.090060671617</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-6989.2345445645587</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10932,8 +11051,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="698340096"/>
-        <c:axId val="698133504"/>
+        <c:axId val="499341568"/>
+        <c:axId val="499339264"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10958,7 +11077,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11144,6 +11263,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11153,7 +11275,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -11339,6 +11461,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11360,11 +11485,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="698092928"/>
-        <c:axId val="698131584"/>
+        <c:axId val="499113344"/>
+        <c:axId val="499283456"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="698092928"/>
+        <c:axId val="499113344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11407,14 +11532,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="698131584"/>
+        <c:crossAx val="499283456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="698131584"/>
+        <c:axId val="499283456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11465,12 +11590,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="698092928"/>
+        <c:crossAx val="499113344"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="698133504"/>
+        <c:axId val="499339264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11507,12 +11632,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="698340096"/>
+        <c:crossAx val="499341568"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="698340096"/>
+        <c:axId val="499341568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11521,7 +11646,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="698133504"/>
+        <c:crossAx val="499339264"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11700,7 +11825,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11886,6 +12011,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11895,7 +12023,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12080,6 +12208,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -12123,7 +12254,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12309,6 +12440,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12318,7 +12452,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12504,6 +12638,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>17163594.417257134</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>17258504.389312655</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12546,7 +12683,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12732,6 +12869,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12741,7 +12881,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12927,6 +13067,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>6275758.643776156</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6370668.6158316769</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12948,11 +13091,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="698451456"/>
-        <c:axId val="698453376"/>
+        <c:axId val="499756032"/>
+        <c:axId val="499761920"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="698451456"/>
+        <c:axId val="499756032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12995,14 +13138,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="698453376"/>
+        <c:crossAx val="499761920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="698453376"/>
+        <c:axId val="499761920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13053,7 +13196,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="698451456"/>
+        <c:crossAx val="499756032"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13265,7 +13408,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13451,6 +13594,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-314574.39222416701</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-61834.682935360193</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13470,8 +13616,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="698992896"/>
-        <c:axId val="698990976"/>
+        <c:axId val="500859264"/>
+        <c:axId val="500857088"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -13496,7 +13642,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13682,6 +13828,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13691,7 +13840,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -13877,6 +14026,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13898,11 +14050,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="698933248"/>
-        <c:axId val="698935168"/>
+        <c:axId val="499923968"/>
+        <c:axId val="500855552"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="698933248"/>
+        <c:axId val="499923968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13945,14 +14097,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="698935168"/>
+        <c:crossAx val="500855552"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="698935168"/>
+        <c:axId val="500855552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14003,12 +14155,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="698933248"/>
+        <c:crossAx val="499923968"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="698990976"/>
+        <c:axId val="500857088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14045,12 +14197,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="698992896"/>
+        <c:crossAx val="500859264"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="698992896"/>
+        <c:axId val="500859264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14059,7 +14211,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="698990976"/>
+        <c:crossAx val="500857088"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14238,7 +14390,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14424,6 +14576,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14433,7 +14588,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14618,6 +14773,9 @@
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>1319095.5916679052</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
               </c:numCache>
@@ -14661,7 +14819,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14847,6 +15005,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14856,7 +15017,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15042,6 +15203,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>2261296.217489922</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2274170.572835926</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15084,7 +15248,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15270,6 +15434,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15279,7 +15446,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15465,6 +15632,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>942200.62582201674</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>955074.98116802075</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15486,11 +15656,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="577734528"/>
-        <c:axId val="577736064"/>
+        <c:axId val="501023872"/>
+        <c:axId val="501025792"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="577734528"/>
+        <c:axId val="501023872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15533,14 +15703,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="577736064"/>
+        <c:crossAx val="501025792"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="577736064"/>
+        <c:axId val="501025792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15591,7 +15761,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="577734528"/>
+        <c:crossAx val="501023872"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15782,7 +15952,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15968,6 +16138,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-48953.662764892986</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-3630.2608901650879</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15987,8 +16160,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="692075520"/>
-        <c:axId val="692073984"/>
+        <c:axId val="490286080"/>
+        <c:axId val="490284544"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -16013,7 +16186,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16199,6 +16372,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16208,7 +16384,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -16394,6 +16570,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16415,11 +16594,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="692066560"/>
-        <c:axId val="692072448"/>
+        <c:axId val="534348160"/>
+        <c:axId val="490283008"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="692066560"/>
+        <c:axId val="534348160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16462,14 +16641,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692072448"/>
+        <c:crossAx val="490283008"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="692072448"/>
+        <c:axId val="490283008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16520,12 +16699,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692066560"/>
+        <c:crossAx val="534348160"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="692073984"/>
+        <c:axId val="490284544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16562,12 +16741,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692075520"/>
+        <c:crossAx val="490286080"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="692075520"/>
+        <c:axId val="490286080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16576,7 +16755,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="692073984"/>
+        <c:crossAx val="490284544"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -16755,7 +16934,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16941,6 +17120,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16950,7 +17132,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17135,6 +17317,9 @@
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>1174811.7958955525</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
               </c:numCache>
@@ -17178,7 +17363,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -17364,6 +17549,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17373,7 +17561,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17559,6 +17747,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1822505.1596172629</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1831898.1745119649</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17601,7 +17792,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -17787,6 +17978,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17796,7 +17990,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17982,6 +18176,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>647693.3637217104</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>657086.3786164124</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18003,11 +18200,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="692607232"/>
-        <c:axId val="692609024"/>
+        <c:axId val="490871040"/>
+        <c:axId val="490876928"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="692607232"/>
+        <c:axId val="490871040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -18050,14 +18247,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692609024"/>
+        <c:crossAx val="490876928"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="692609024"/>
+        <c:axId val="490876928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -18108,7 +18305,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692607232"/>
+        <c:crossAx val="490871040"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -19044,7 +19241,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -19175,28 +19372,28 @@
       </c>
       <c r="M3" s="27"/>
       <c r="P3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="46" t="s">
+      <c r="R3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="R3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="W3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="W3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -21761,6 +21958,44 @@
       </c>
       <c r="L64" s="29">
         <v>337060.4799167217</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="32">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="31">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="29">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="29">
+        <v>-34946.17272282279</v>
+      </c>
+      <c r="F65" s="30">
+        <v>-31369.994514880033</v>
+      </c>
+      <c r="G65" s="30">
+        <v>1284979.7395587955</v>
+      </c>
+      <c r="H65" s="30">
+        <v>1431467.3820758634</v>
+      </c>
+      <c r="I65" s="30">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J65" s="30">
+        <v>1803474.034715408</v>
+      </c>
+      <c r="K65" s="30">
+        <v>644981.0052331842</v>
+      </c>
+      <c r="L65" s="29">
+        <v>372006.65263954451</v>
       </c>
     </row>
   </sheetData>
@@ -21779,7 +22014,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH64"/>
+  <dimension ref="A1:AH65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -21814,10 +22049,10 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>3</v>
@@ -21850,16 +22085,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N1" s="44" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -21921,28 +22156,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="46" t="s">
+      <c r="S3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="S3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="X3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -25221,6 +25456,56 @@
       </c>
       <c r="P64" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="16">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="17">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="17">
+        <v>-6989.2345445645587</v>
+      </c>
+      <c r="F65" s="18">
+        <v>-6273.9989029760072</v>
+      </c>
+      <c r="G65" s="18">
+        <v>1613024.4036469234</v>
+      </c>
+      <c r="H65" s="18">
+        <v>1796909.1256689748</v>
+      </c>
+      <c r="I65" s="18">
+        <v>1319891.5920995933</v>
+      </c>
+      <c r="J65" s="18">
+        <v>2032514.2354846764</v>
+      </c>
+      <c r="K65" s="18">
+        <v>712622.64338508318</v>
+      </c>
+      <c r="L65" s="17">
+        <v>235605.10981570161</v>
+      </c>
+      <c r="M65" s="22">
+        <v>2.9890860469234198E-2</v>
+      </c>
+      <c r="N65" s="22">
+        <v>5.7377062222749194E-2</v>
+      </c>
+      <c r="O65" s="22">
+        <v>52.095487833085492</v>
+      </c>
+      <c r="P65" s="1">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -25239,7 +25524,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH64"/>
+  <dimension ref="A1:AH65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -25274,10 +25559,10 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>3</v>
@@ -25310,16 +25595,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N1" s="44" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -25381,28 +25666,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="46" t="s">
+      <c r="S3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="S3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="X3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -28681,6 +28966,56 @@
       </c>
       <c r="P64" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="16">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="17">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="17">
+        <v>-61834.682935360193</v>
+      </c>
+      <c r="F65" s="18">
+        <v>-55506.898563595001</v>
+      </c>
+      <c r="G65" s="18">
+        <v>13503119.648860516</v>
+      </c>
+      <c r="H65" s="18">
+        <v>15042474.786605056</v>
+      </c>
+      <c r="I65" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J65" s="18">
+        <v>17258504.389312655</v>
+      </c>
+      <c r="K65" s="18">
+        <v>6370668.6158316769</v>
+      </c>
+      <c r="L65" s="17">
+        <v>2216029.6027075993</v>
+      </c>
+      <c r="M65" s="22">
+        <v>2.9890860469234198E-2</v>
+      </c>
+      <c r="N65" s="22">
+        <v>5.7377062222749194E-2</v>
+      </c>
+      <c r="O65" s="22">
+        <v>52.095487833085492</v>
+      </c>
+      <c r="P65" s="1">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -28699,7 +29034,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ64"/>
+  <dimension ref="A1:AJ65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -28734,10 +29069,10 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>3</v>
@@ -28746,10 +29081,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -28776,16 +29111,16 @@
         <v>12</v>
       </c>
       <c r="O1" s="44" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P1" s="44" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q1" s="48" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -28859,28 +29194,28 @@
       <c r="P3" s="22"/>
       <c r="Q3" s="22"/>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -32525,6 +32860,62 @@
       </c>
       <c r="R64" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="16">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="17">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="17">
+        <v>1687200</v>
+      </c>
+      <c r="F65" s="17">
+        <v>4001533.5447742641</v>
+      </c>
+      <c r="G65" s="17">
+        <v>-3630.2608901650879</v>
+      </c>
+      <c r="H65" s="18">
+        <v>-3258.762128697666</v>
+      </c>
+      <c r="I65" s="18">
+        <v>1835942.877011803</v>
+      </c>
+      <c r="J65" s="18">
+        <v>2045240.2967063773</v>
+      </c>
+      <c r="K65" s="18">
+        <v>1319095.5916679052</v>
+      </c>
+      <c r="L65" s="18">
+        <v>2274170.572835926</v>
+      </c>
+      <c r="M65" s="18">
+        <v>955074.98116802075</v>
+      </c>
+      <c r="N65" s="17">
+        <v>228930.27612954858</v>
+      </c>
+      <c r="O65" s="22">
+        <v>2.9890860469234198E-2</v>
+      </c>
+      <c r="P65" s="22">
+        <v>5.7377062222749194E-2</v>
+      </c>
+      <c r="Q65" s="22">
+        <v>52.095487833085492</v>
+      </c>
+      <c r="R65" s="1">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -32543,7 +32934,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ64"/>
+  <dimension ref="A1:AJ65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -32578,10 +32969,10 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>3</v>
@@ -32614,19 +33005,19 @@
         <v>12</v>
       </c>
       <c r="M1" s="48" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N1" s="48" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P1" s="48" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -32704,28 +33095,28 @@
         <v>1</v>
       </c>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -36189,6 +36580,59 @@
         <v>53.045574900238108</v>
       </c>
       <c r="Q64" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="16">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="17">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="17">
+        <v>-34946.17272282279</v>
+      </c>
+      <c r="F65" s="18">
+        <v>-31369.994514880033</v>
+      </c>
+      <c r="G65" s="18">
+        <v>1310495.1262244673</v>
+      </c>
+      <c r="H65" s="18">
+        <v>1459891.5218724203</v>
+      </c>
+      <c r="I65" s="18">
+        <v>1174811.7958955525</v>
+      </c>
+      <c r="J65" s="18">
+        <v>1831898.1745119649</v>
+      </c>
+      <c r="K65" s="18">
+        <v>657086.3786164124</v>
+      </c>
+      <c r="L65" s="17">
+        <v>372006.65263954451</v>
+      </c>
+      <c r="M65" s="21">
+        <v>31.202982920806502</v>
+      </c>
+      <c r="N65" s="21">
+        <v>57.963077631244182</v>
+      </c>
+      <c r="O65" s="21">
+        <v>72.982292563465052</v>
+      </c>
+      <c r="P65" s="21">
+        <v>27.924647766802451</v>
+      </c>
+      <c r="Q65" s="1">
         <v>1</v>
       </c>
     </row>
@@ -36208,7 +36652,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ64"/>
+  <dimension ref="A1:AJ65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -36243,10 +36687,10 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>3</v>
@@ -36255,10 +36699,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -36354,28 +36798,28 @@
       </c>
       <c r="O3" s="7"/>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -39306,6 +39750,50 @@
       </c>
       <c r="N64" s="17">
         <v>1962766.6496992977</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="16">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="17">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="17">
+        <v>1687200</v>
+      </c>
+      <c r="F65" s="17">
+        <v>4001533.5447742641</v>
+      </c>
+      <c r="G65" s="17">
+        <v>-130359.36832865544</v>
+      </c>
+      <c r="H65" s="18">
+        <v>-117019.18553050711</v>
+      </c>
+      <c r="I65" s="18">
+        <v>10978430.576441985</v>
+      </c>
+      <c r="J65" s="18">
+        <v>12229971.253832327</v>
+      </c>
+      <c r="K65" s="18">
+        <v>8275639.9932962749</v>
+      </c>
+      <c r="L65" s="18">
+        <v>14323097.271860281</v>
+      </c>
+      <c r="M65" s="18">
+        <v>6047457.2785640061</v>
+      </c>
+      <c r="N65" s="17">
+        <v>2093126.0180279531</v>
       </c>
     </row>
   </sheetData>
@@ -39324,7 +39812,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -39359,16 +39847,16 @@
   <sheetData>
     <row r="1" spans="1:33" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -39455,28 +39943,28 @@
       </c>
       <c r="M3" s="7"/>
       <c r="P3" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="46" t="s">
+      <c r="R3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="R3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="W3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="W3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -42041,6 +42529,44 @@
       </c>
       <c r="L64" s="17">
         <v>2786404.2807864728</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="16">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="17">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="17">
+        <v>-309173.41467680095</v>
+      </c>
+      <c r="F65" s="18">
+        <v>-277534.492817975</v>
+      </c>
+      <c r="G65" s="18">
+        <v>10700270.628994567</v>
+      </c>
+      <c r="H65" s="18">
+        <v>11920101.082721591</v>
+      </c>
+      <c r="I65" s="18">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J65" s="18">
+        <v>15015678.778184865</v>
+      </c>
+      <c r="K65" s="18">
+        <v>5654343.9604574405</v>
+      </c>
+      <c r="L65" s="17">
+        <v>3095577.6954632737</v>
       </c>
     </row>
   </sheetData>
